--- a/Config/Datas/Tables/z_战斗表现_CombatPresentationConfig.xlsx
+++ b/Config/Datas/Tables/z_战斗表现_CombatPresentationConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CombatPresentationConfig" sheetId="1" r:id="R95d69ea5718c4229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CombatPresentationConfig" sheetId="1" r:id="Rf5b293ffc1654767"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,12 +40,22 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -138,7 +148,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -274,6 +284,21 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -541,6 +566,16 @@
     <x:col min="44" max="44" width="28.75" hidden="0" customWidth="1"/>
     <x:col min="45" max="45" width="28.75" hidden="0" customWidth="1"/>
     <x:col min="46" max="46" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="50" max="50" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="51" max="51" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="52" max="52" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="53" max="53" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="54" max="54" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="55" max="55" width="28.75" hidden="0" customWidth="1"/>
+    <x:col min="56" max="56" width="28.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="46" customHeight="1">
@@ -694,6 +729,41 @@
       <x:c r="AT1" s="38" t="str">
         <x:v>healthBarHeightPixels</x:v>
       </x:c>
+      <x:c r="AU1" s="43" t="str">
+        <x:v>healthBarFrameResourceId</x:v>
+      </x:c>
+      <x:c r="AV1" s="43" t="str">
+        <x:v>healthBarFillResourceId</x:v>
+      </x:c>
+      <x:c r="AW1" s="43" t="str">
+        <x:v>damageNumberAtlasResourceId</x:v>
+      </x:c>
+      <x:c r="AX1" s="43" t="str">
+        <x:v>damageNumberGlyphs</x:v>
+      </x:c>
+      <x:c r="AY1" s="43" t="str">
+        <x:v>damageNumberRiseDurationMilli</x:v>
+      </x:c>
+      <x:c r="AZ1" s="43" t="str">
+        <x:v>damageNumberRiseHeightPixels</x:v>
+      </x:c>
+      <x:c r="BA1" s="43" t="str">
+        <x:v>damageNumberScaleStartPermille</x:v>
+      </x:c>
+      <x:c r="BB1" s="43" t="str">
+        <x:v>damageNumberScaleEndPermille</x:v>
+      </x:c>
+      <x:c r="BC1" s="43" t="str">
+        <x:v>damageNumberKerningPermille</x:v>
+      </x:c>
+      <x:c r="BD1" s="43" t="str">
+        <x:v>damageNumberGlyphScalePermille</x:v>
+      </x:c>
+      <x:c r="BE1" t="inlineStr">
+        <x:is>
+          <x:t>renderConfigIds</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -845,6 +915,41 @@
       </x:c>
       <x:c r="AT2" s="39" t="str">
         <x:v>float</x:v>
+      </x:c>
+      <x:c r="AU2" s="44" t="str">
+        <x:v>int#ref=TbResource</x:v>
+      </x:c>
+      <x:c r="AV2" s="44" t="str">
+        <x:v>int#ref=TbResource</x:v>
+      </x:c>
+      <x:c r="AW2" s="44" t="str">
+        <x:v>int#ref=TbResource</x:v>
+      </x:c>
+      <x:c r="AX2" s="44" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AY2" s="44" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AZ2" s="44" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="BA2" s="44" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="BB2" s="44" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="BC2" s="44" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="BD2" s="44" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="BE2" t="inlineStr">
+        <x:is>
+          <x:t>(list#sep=;),int#ref=TbCombatRender</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -896,6 +1001,16 @@
       <x:c r="AR3" s="24" t="str"/>
       <x:c r="AS3" s="24" t="str"/>
       <x:c r="AT3" s="24" t="str"/>
+      <x:c r="AU3" s="24"/>
+      <x:c r="AV3" s="24"/>
+      <x:c r="AW3" s="24"/>
+      <x:c r="AX3" s="24"/>
+      <x:c r="AY3" s="24"/>
+      <x:c r="AZ3" s="24"/>
+      <x:c r="BA3" s="24"/>
+      <x:c r="BB3" s="24"/>
+      <x:c r="BC3" s="24"/>
+      <x:c r="BD3" s="24"/>
     </x:row>
     <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="8" t="str">
@@ -1047,6 +1162,41 @@
       </x:c>
       <x:c r="AT4" s="24" t="str">
         <x:v>战斗血条最终显示高度；由 CombatHealthBar Prefab 导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="AU4" s="24" t="str">
+        <x:v>血条底框纹理资源；引用 TbResource Texture。</x:v>
+      </x:c>
+      <x:c r="AV4" s="24" t="str">
+        <x:v>血条填充纹理资源；引用 TbResource Texture。</x:v>
+      </x:c>
+      <x:c r="AW4" s="24" t="str">
+        <x:v>伤害数字横向等分图集；引用 TbResource Texture。</x:v>
+      </x:c>
+      <x:c r="AX4" s="24" t="str">
+        <x:v>伤害数字图集从左到右的字符顺序；字符必须唯一并包含 0-9。</x:v>
+      </x:c>
+      <x:c r="AY4" s="24" t="str">
+        <x:v>伤害数字上升动画持续秒数；原单位×1000存整数，实际值=表值/1000。</x:v>
+      </x:c>
+      <x:c r="AZ4" s="24" t="str">
+        <x:v>伤害数字上升距离；逻辑像素，运行时按战斗规则转换世界单位。</x:v>
+      </x:c>
+      <x:c r="BA4" s="24" t="str">
+        <x:v>伤害数字动画起始缩放；千分比，1000=1倍。</x:v>
+      </x:c>
+      <x:c r="BB4" s="24" t="str">
+        <x:v>伤害数字动画结束缩放；千分比，1000=1倍。</x:v>
+      </x:c>
+      <x:c r="BC4" s="24" t="str">
+        <x:v>相邻伤害数字字形间距；千分比，1000=完整字宽。</x:v>
+      </x:c>
+      <x:c r="BD4" s="24" t="str">
+        <x:v>伤害数字字形基础缩放；千分比，1000=图集原始逻辑像素尺寸。</x:v>
+      </x:c>
+      <x:c r="BE4" t="inlineStr">
+        <x:is>
+          <x:t>模型与技能片段层级绑定目录；运行时必须显式匹配，不使用统一层级回退。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
@@ -1186,6 +1336,41 @@
       <x:c r="AT5" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="AU5" s="24" t="n">
+        <x:v>960006</x:v>
+      </x:c>
+      <x:c r="AV5" s="24" t="n">
+        <x:v>960007</x:v>
+      </x:c>
+      <x:c r="AW5" s="24" t="n">
+        <x:v>960008</x:v>
+      </x:c>
+      <x:c r="AX5" s="24" t="str">
+        <x:v>./0123456789</x:v>
+      </x:c>
+      <x:c r="AY5" s="24" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="AZ5" s="24" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="BA5" s="24" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="BB5" s="24" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="BC5" s="24" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="BD5" s="24" t="n">
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="BE5" t="inlineStr">
+        <x:is>
+          <x:t>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;98;99;100;101;102;103;104;105;106;107;108;109;110;1001;1002;1003;1004;1005;1006;1007;1008;1009;1010;1011;1012;1013;1014;1015;1016;1017;1018;1019;1020;1021;1022</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/z_战斗表现_CombatPresentationConfig.xlsx
+++ b/Config/Datas/Tables/z_战斗表现_CombatPresentationConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CombatPresentationConfig" sheetId="1" r:id="Rf5b293ffc1654767"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CombatPresentationConfig" sheetId="1" r:id="R627bc934322c4705"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -761,8 +761,26 @@
       </x:c>
       <x:c r="BE1" t="inlineStr">
         <x:is>
-          <x:t>renderConfigIds</x:t>
-        </x:is>
+          <x:t xml:space="preserve">renderConfigIds</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BF1" t="str">
+        <x:v>arenaBoundaryDefaultVisible</x:v>
+      </x:c>
+      <x:c r="BG1" t="str">
+        <x:v>arenaBoundaryColor</x:v>
+      </x:c>
+      <x:c r="BH1" t="str">
+        <x:v>arenaBoundaryWidthPixels</x:v>
+      </x:c>
+      <x:c r="BI1" t="str">
+        <x:v>arenaBoundarySortingOrder</x:v>
+      </x:c>
+      <x:c r="BJ1" t="str">
+        <x:v>arenaBoundaryRenderQueue</x:v>
+      </x:c>
+      <x:c r="BK1" t="str">
+        <x:v>arenaBoundaryShaderName</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
@@ -948,8 +966,26 @@
       </x:c>
       <x:c r="BE2" t="inlineStr">
         <x:is>
-          <x:t>(list#sep=;),int#ref=TbCombatRender</x:t>
-        </x:is>
+          <x:t xml:space="preserve">(list#sep=;),int#ref=TbCombatRender</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BF2" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="BG2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="BH2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="BI2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="BJ2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="BK2" t="str">
+        <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -1011,6 +1047,12 @@
       <x:c r="BB3" s="24"/>
       <x:c r="BC3" s="24"/>
       <x:c r="BD3" s="24"/>
+      <x:c r="BF3"/>
+      <x:c r="BG3"/>
+      <x:c r="BH3"/>
+      <x:c r="BI3"/>
+      <x:c r="BJ3"/>
+      <x:c r="BK3"/>
     </x:row>
     <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="8" t="str">
@@ -1195,8 +1237,26 @@
       </x:c>
       <x:c r="BE4" t="inlineStr">
         <x:is>
-          <x:t>模型与技能片段层级绑定目录；运行时必须显式匹配，不使用统一层级回退。</x:t>
-        </x:is>
+          <x:t xml:space="preserve">模型与技能片段层级绑定目录；运行时必须显式匹配，不使用统一层级回退。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="BF4" t="str">
+        <x:v>战斗地图行走边界默认显示；供统一运行时开关初始化</x:v>
+      </x:c>
+      <x:c r="BG4" t="str">
+        <x:v>真实行走边界线颜色</x:v>
+      </x:c>
+      <x:c r="BH4" t="str">
+        <x:v>边界线宽，显示像素，不改变行走范围</x:v>
+      </x:c>
+      <x:c r="BI4" t="str">
+        <x:v>世界边界线排序，低于屏幕覆盖HUD</x:v>
+      </x:c>
+      <x:c r="BJ4" t="str">
+        <x:v>世界边界线材质渲染队列</x:v>
+      </x:c>
+      <x:c r="BK4" t="str">
+        <x:v>边界线正式引擎Shader标识</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
@@ -1366,10 +1426,26 @@
       <x:c r="BD5" s="24" t="n">
         <x:v>1250</x:v>
       </x:c>
-      <x:c r="BE5" t="inlineStr">
-        <x:is>
-          <x:t>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;98;99;100;101;102;103;104;105;106;107;108;109;110;1001;1002;1003;1004;1005;1006;1007;1008;1009;1010;1011;1012;1013;1014;1015;1016;1017;1018;1019;1020;1021;1022</x:t>
-        </x:is>
+      <x:c r="BE5" t="str">
+        <x:v>1;2;3;4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;98;99;100;101;102;103;104;105;106;107;108;109;110;1001;1002;1003;1004;1005;1006;1007;1008;1009;1010;1011;1012;1013;1014;1015;1016;1017;1020;1021;1022;1101;1102;1103;1104;1105;1106</x:v>
+      </x:c>
+      <x:c r="BF5" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG5" t="str">
+        <x:v>#FF0000</x:v>
+      </x:c>
+      <x:c r="BH5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BI5" t="n">
+        <x:v>32767</x:v>
+      </x:c>
+      <x:c r="BJ5" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="BK5" t="str">
+        <x:v>Sprites/Default</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
